--- a/19/1 Excel/VbaMacro/01 Introduction/abc.xlsx
+++ b/19/1 Excel/VbaMacro/01 Introduction/abc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -332,7 +332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
